--- a/seo/SEO_KEYWORD_MASTER.xlsx
+++ b/seo/SEO_KEYWORD_MASTER.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2734" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="518">
   <si>
     <t>Rank</t>
   </si>
@@ -158,7 +158,7 @@
     <t>/services/extension</t>
   </si>
   <si>
-    <t>business_value 85/100, cluster avec estimation de prix sourcée (La Maison Des Travaux) disponible pour enrichir le contenu.</t>
+    <t>business_value 85/100, cible /services/extension — pas de contenu tarifaire (décision client 2026-08-20), le contenu reste centré sur le savoir-faire et les réalisations.</t>
   </si>
   <si>
     <t>devis rénovation maison gratuit</t>
@@ -434,7 +434,7 @@
     <t>rénovation complète maison Toulouse</t>
   </si>
   <si>
-    <t>Cluster prioritaire n°1 : c'est le service le plus recherché et le mieux documenté chez les concurrents (FAQ, avant/après). Une seule page cible pour éviter la cannibalisation entre les variantes. | Used On Website: Le mot "complète" n'apparaît pas sur /services/renovation (il apparaît sur /guides/prix-renovation-maison). La page service couvre le même périmètre ("rénovation intérieure et extérieure") sans utiliser ce mot exact. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
+    <t>Cluster prioritaire n°1 : c'est le service le plus recherché et le mieux documenté chez les concurrents (FAQ, avant/après). Une seule page cible pour éviter la cannibalisation entre les variantes. | Used On Website: Le mot "complète" n'apparaît pas sur /services/renovation. La page service couvre le même périmètre ("rénovation intérieure et extérieure") sans utiliser ce mot exact. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
   </si>
   <si>
     <t>K019</t>
@@ -500,7 +500,10 @@
     <t>prix maçonnerie Toulouse</t>
   </si>
   <si>
-    <t>'Maçon Toulouse' est dominé par des annuaires (PagesJaunes, Travaux.com) en plus des concurrents directs — la fiche Google Business Profile compte autant que la page web ici | Used On Website: Aucune mention de prix sur /services/maconnerie (le prix est traité uniquement sur /guides/prix-maconnerie, page nationale sans ancrage Toulouse). Gap identifié — voir CONTENT_GAPS. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
+    <t>Research/Opportunity Only — no customer-facing pricing (client decision, 2026-08-20)</t>
+  </si>
+  <si>
+    <t>'Maçon Toulouse' est dominé par des annuaires (PagesJaunes, Travaux.com) en plus des concurrents directs — la fiche Google Business Profile compte autant que la page web ici | Used On Website: Mot-clé "prix" — NE PAS créer de contenu tarifaire client (décision client, 2026-08-20). Conservé comme mot-clé de recherche/opportunité uniquement, sans page cible sur le site actuel. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
   </si>
   <si>
     <t>K028</t>
@@ -542,7 +545,7 @@
     <t>prix terrassement Toulouse</t>
   </si>
   <si>
-    <t>Souvent recherché en combo avec dallage — envisager un maillage fort entre les deux pages plutôt qu'une fusion (services distincts et réellement proposés séparément) | Used On Website: Aucune mention de prix sur /services/terrassement (traité uniquement sur /guides/prix-terrassement, page nationale sans ancrage Toulouse). Gap identifié — voir CONTENT_GAPS. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
+    <t>Souvent recherché en combo avec dallage — envisager un maillage fort entre les deux pages plutôt qu'une fusion (services distincts et réellement proposés séparément) | Used On Website: Mot-clé "prix" — NE PAS créer de contenu tarifaire client (décision client, 2026-08-20). Conservé comme mot-clé de recherche/opportunité uniquement, sans page cible sur le site actuel. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
   </si>
   <si>
     <t>K033</t>
@@ -584,7 +587,7 @@
     <t>prix dalle béton m2</t>
   </si>
   <si>
-    <t>Marché avec des spécialistes purs (dallage-toulouse.com) — RK doit démontrer des réalisations réelles pour rivaliser | Used On Website: Aucune mention de prix sur /services/dallage, et aucun guide de prix dédié au dallage n'existe (contrairement à rénovation/construction/maçonnerie/terrassement). Gap identifié — voir CONTENT_GAPS. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
+    <t>Marché avec des spécialistes purs (dallage-toulouse.com) — RK doit démontrer des réalisations réelles pour rivaliser | Used On Website: Mot-clé "prix" — NE PAS créer de contenu tarifaire client (décision client, 2026-08-20). Conservé comme mot-clé de recherche/opportunité uniquement, sans page cible sur le site actuel. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
   </si>
   <si>
     <t>K039</t>
@@ -611,7 +614,7 @@
     <t>prix extension maison Toulouse</t>
   </si>
   <si>
-    <t>ESTIMATE de prix trouvée via recherche (source La Maison Des Travaux, août 2026) : extension 2 pans ~1275-2850€/m2 à Toulouse. À citer avec la source, jamais présenté comme un prix RK Pyrénées tant que non confirmé par vous. | Used On Website: Aucune mention de prix sur /services/extension, et aucun guide de prix dédié à l'extension n'existe. Une fourchette de prix sourcée (La Maison Des Travaux) existe dans les notes de recherche mais n'a pas été confirmée par le client pour publication — voir KEYWORD_CLUSTERING.md. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
+    <t>ESTIMATE de prix trouvée via recherche (source La Maison Des Travaux, août 2026) : extension 2 pans ~1275-2850€/m2 à Toulouse. À citer avec la source, jamais présenté comme un prix RK Pyrénées tant que non confirmé par vous. | Used On Website: Mot-clé "prix" — NE PAS créer de contenu tarifaire client (décision client, 2026-08-20). Conservé comme mot-clé de recherche/opportunité uniquement, sans page cible sur le site actuel. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
   </si>
   <si>
     <t>K042</t>
@@ -620,9 +623,6 @@
     <t>extension maison prix m2</t>
   </si>
   <si>
-    <t>ESTIMATE de prix trouvée via recherche (source La Maison Des Travaux, août 2026) : extension 2 pans ~1275-2850€/m2 à Toulouse. À citer avec la source, jamais présenté comme un prix RK Pyrénées tant que non confirmé par vous. | Used On Website: Même gap que "prix extension maison Toulouse" — voir CONTENT_GAPS. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
-  </si>
-  <si>
     <t>K043</t>
   </si>
   <si>
@@ -710,9 +710,6 @@
     <t>P2</t>
   </si>
   <si>
-    <t>/guides/prix-renovation-maison</t>
-  </si>
-  <si>
     <t>guide informationnel</t>
   </si>
   <si>
@@ -722,7 +719,7 @@
     <t>Effy, Hellowatt, Architecteo, Manda, travaux.com — sites médias/leads nationaux</t>
   </si>
   <si>
-    <t>ESTIMATE trouvée via recherche (sources Effy/Hellowatt/Architecteo, 2026) : ~700€/m2 en moyenne, 160-350€/m2 rafraîchissement léger, 950-1250€/m2+ rénovation complète, jusqu'à 4000€/m2 rénovation lourde. Toujours citer la source, jamais présenté comme un devis RK. | Used On Website: Confirmé : "m²" apparaît 14 fois sur /guides/prix-renovation-maison avec de vraies fourchettes sourcées. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
+    <t>ESTIMATE trouvée via recherche (sources Effy/Hellowatt/Architecteo, 2026) : ~700€/m2 en moyenne, 160-350€/m2 rafraîchissement léger, 950-1250€/m2+ rénovation complète, jusqu'à 4000€/m2 rénovation lourde. Toujours citer la source, jamais présenté comme un devis RK. | Used On Website: Mot-clé "prix" — NE PAS créer de contenu tarifaire client (décision client, 2026-08-20). Conservé comme mot-clé de recherche/opportunité uniquement, sans page cible sur le site actuel. L'ancien guide /guides/prix-renovation-maison (qui citait de vraies fourchettes sourcées) a été retiré et remplacé par /guides/etapes-renovation-maison (sans aucun chiffre). | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
   </si>
   <si>
     <t>K050</t>
@@ -737,7 +734,7 @@
     <t>Voir COMPETITOR_ANALYSIS.md</t>
   </si>
   <si>
-    <t>Variante question — même page cible que ci-dessus, ne pas dupliquer | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
+    <t>Variante question — même page cible que ci-dessus, ne pas dupliquer | Used On Website: Mot-clé "prix" — NE PAS créer de contenu tarifaire client (décision client, 2026-08-20). Conservé comme mot-clé de recherche/opportunité uniquement, sans page cible sur le site actuel. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
   </si>
   <si>
     <t>K051</t>
@@ -752,7 +749,7 @@
     <t>PAA</t>
   </si>
   <si>
-    <t>Variante question — même page cible | Used On Website: Correspondance sémantique (racine "rénov-" + "budget" présents sur /guides/prix-renovation-maison) ; la forme verbale exacte "rénover" et le mot "quel" n'apparaissent pas littéralement. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
+    <t>Variante question — même page cible | Used On Website: Mot-clé "prix" — NE PAS créer de contenu tarifaire client (décision client, 2026-08-20). Conservé comme mot-clé de recherche/opportunité uniquement, sans page cible sur le site actuel. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
   </si>
   <si>
     <t>K052</t>
@@ -767,13 +764,10 @@
     <t>élevée (constructeurs nationaux)</t>
   </si>
   <si>
-    <t>/guides/prix-construction-maison</t>
-  </si>
-  <si>
     <t>constructeurs nationaux</t>
   </si>
   <si>
-    <t>Volume national probable élevé mais concurrence de constructeurs catalogue avec gros budgets SEO | Used On Website: Confirmé : "m²" présent sur /guides/prix-construction-maison. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
+    <t>Volume national probable élevé mais concurrence de constructeurs catalogue avec gros budgets SEO | Used On Website: Mot-clé "prix" — NE PAS créer de contenu tarifaire client (décision client, 2026-08-20). Conservé comme mot-clé de recherche/opportunité uniquement, sans page cible sur le site actuel. Ancien guide /guides/prix-construction-maison retiré, remplacé par /guides/etapes-projet-construction. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
   </si>
   <si>
     <t>K053</t>
@@ -794,10 +788,7 @@
     <t>moyenne</t>
   </si>
   <si>
-    <t>/guides/prix-maconnerie</t>
-  </si>
-  <si>
-    <t>Bonne opportunité: moins de guides dédiés trouvés que pour la rénovation générale | Used On Website: Confirmé : "m²" présent sur /guides/prix-maconnerie. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
+    <t>Bonne opportunité: moins de guides dédiés trouvés que pour la rénovation générale | Used On Website: Mot-clé "prix" — NE PAS créer de contenu tarifaire client (décision client, 2026-08-20). Conservé comme mot-clé de recherche/opportunité uniquement, sans page cible sur le site actuel. Ancien guide /guides/prix-maconnerie retiré, remplacé par /guides/comment-choisir-entreprise-maconnerie-toulouse. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
   </si>
   <si>
     <t>K054</t>
@@ -812,10 +803,7 @@
     <t>55/100 (MEDIUM)</t>
   </si>
   <si>
-    <t>/guides/prix-terrassement</t>
-  </si>
-  <si>
-    <t>Peu de guides dédiés trouvés spécifiquement — opportunité de contenu original | Used On Website: Confirmé : "m²" présent sur /guides/prix-terrassement. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
+    <t>Peu de guides dédiés trouvés spécifiquement — opportunité de contenu original | Used On Website: Mot-clé "prix" — NE PAS créer de contenu tarifaire client (décision client, 2026-08-20). Conservé comme mot-clé de recherche/opportunité uniquement, sans page cible sur le site actuel. Ancien guide /guides/prix-terrassement retiré, remplacé par /guides/comment-preparer-chantier-terrassement. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
   </si>
   <si>
     <t>K055</t>
@@ -827,7 +815,7 @@
     <t>15</t>
   </si>
   <si>
-    <t>Variante question, même page cible que 'prix maçonnerie au m2' | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
+    <t>Variante question, même page cible que 'prix maçonnerie au m2' | Used On Website: Mot-clé "prix" — NE PAS créer de contenu tarifaire client (décision client, 2026-08-20). Conservé comme mot-clé de recherche/opportunité uniquement, sans page cible sur le site actuel. | Commercial Intent / Local Intent : scores qualitatifs 0-100 attribués par le chercheur (estimation de pertinence), PAS une donnée mesurée par un outil Ads/Analytics — voir Data Type.</t>
   </si>
   <si>
     <t>K056</t>
@@ -1088,6 +1076,123 @@
     <t>rénovation maison Genève</t>
   </si>
   <si>
+    <t>K076</t>
+  </si>
+  <si>
+    <t>étapes rénovation maison Toulouse</t>
+  </si>
+  <si>
+    <t>INFORMATIONAL_ETAPES_RENOVATION</t>
+  </si>
+  <si>
+    <t>N/A — non recherché (nouveau sujet, remplace un guide de prix retiré)</t>
+  </si>
+  <si>
+    <t>N/A (nouveau)</t>
+  </si>
+  <si>
+    <t>/guides/etapes-renovation-maison</t>
+  </si>
+  <si>
+    <t>guide pratique (sans prix)</t>
+  </si>
+  <si>
+    <t>PAA (probable, non vérifié)</t>
+  </si>
+  <si>
+    <t>N/A — non recherché</t>
+  </si>
+  <si>
+    <t>Active — nouveau (remplace un guide de prix retiré, décision client 2026-08-20)</t>
+  </si>
+  <si>
+    <t>Client-provided (directive de stratégie de contenu, 2026-08-20)</t>
+  </si>
+  <si>
+    <t>Sujet fourni directement par le client pour remplacer le contenu tarifaire retiré. Représenté sur /guides/etapes-renovation-maison (vérifié).</t>
+  </si>
+  <si>
+    <t>K077</t>
+  </si>
+  <si>
+    <t>comment préparer un projet de rénovation</t>
+  </si>
+  <si>
+    <t>K078</t>
+  </si>
+  <si>
+    <t>rénovation maison ancienne étapes</t>
+  </si>
+  <si>
+    <t>INFORMATIONAL_RENOVATION_ANCIENNE</t>
+  </si>
+  <si>
+    <t>/guides/renovation-maison-ancienne-etapes</t>
+  </si>
+  <si>
+    <t>Sujet fourni directement par le client pour remplacer le contenu tarifaire retiré. Représenté sur /guides/renovation-maison-ancienne-etapes (vérifié).</t>
+  </si>
+  <si>
+    <t>K079</t>
+  </si>
+  <si>
+    <t>étapes projet construction Toulouse</t>
+  </si>
+  <si>
+    <t>INFORMATIONAL_ETAPES_CONSTRUCTION</t>
+  </si>
+  <si>
+    <t>/guides/etapes-projet-construction</t>
+  </si>
+  <si>
+    <t>Sujet fourni directement par le client pour remplacer le contenu tarifaire retiré. Représenté sur /guides/etapes-projet-construction (vérifié).</t>
+  </si>
+  <si>
+    <t>K080</t>
+  </si>
+  <si>
+    <t>comment choisir une entreprise de maçonnerie Toulouse</t>
+  </si>
+  <si>
+    <t>INFORMATIONAL_CHOIX_MACONNERIE</t>
+  </si>
+  <si>
+    <t>/guides/comment-choisir-entreprise-maconnerie-toulouse</t>
+  </si>
+  <si>
+    <t>Sujet fourni directement par le client pour remplacer le contenu tarifaire retiré. Représenté sur /guides/comment-choisir-entreprise-maconnerie-toulouse (vérifié).</t>
+  </si>
+  <si>
+    <t>K081</t>
+  </si>
+  <si>
+    <t>comment préparer un chantier de terrassement</t>
+  </si>
+  <si>
+    <t>INFORMATIONAL_PREPARER_TERRASSEMENT</t>
+  </si>
+  <si>
+    <t>/guides/comment-preparer-chantier-terrassement</t>
+  </si>
+  <si>
+    <t>Sujet fourni directement par le client pour remplacer le contenu tarifaire retiré. Représenté sur /guides/comment-preparer-chantier-terrassement (vérifié).</t>
+  </si>
+  <si>
+    <t>K082</t>
+  </si>
+  <si>
+    <t>comment choisir un professionnel pour un dallage extérieur</t>
+  </si>
+  <si>
+    <t>INFORMATIONAL_CHOIX_DALLAGE</t>
+  </si>
+  <si>
+    <t>/guides/comment-choisir-professionnel-dallage-exterieur</t>
+  </si>
+  <si>
+    <t>Sujet fourni directement par le client pour remplacer le contenu tarifaire retiré. Représenté sur /guides/comment-choisir-professionnel-dallage-exterieur (vérifié).</t>
+  </si>
+  <si>
     <t>Primary Page</t>
   </si>
   <si>
@@ -1193,9 +1298,6 @@
     <t>devis maçon à Toulouse</t>
   </si>
   <si>
-    <t>prix maçonnerie à Toulouse</t>
-  </si>
-  <si>
     <t>artisan maçon à Toulouse</t>
   </si>
   <si>
@@ -1208,9 +1310,6 @@
     <t>terrassement maison à Toulouse</t>
   </si>
   <si>
-    <t>prix terrassement à Toulouse</t>
-  </si>
-  <si>
     <t>devis terrassement à Toulouse</t>
   </si>
   <si>
@@ -1226,21 +1325,12 @@
     <t>dallage extérieur à Toulouse</t>
   </si>
   <si>
-    <t>prix dalle béton m2 à Toulouse</t>
-  </si>
-  <si>
     <t>extension maison à Toulouse</t>
   </si>
   <si>
     <t>agrandissement maison à Toulouse</t>
   </si>
   <si>
-    <t>prix extension maison à Toulouse</t>
-  </si>
-  <si>
-    <t>extension maison prix m2 à Toulouse</t>
-  </si>
-  <si>
     <t>entreprise extension maison à Toulouse</t>
   </si>
   <si>
@@ -1259,27 +1349,6 @@
     <t>création allée à Toulouse</t>
   </si>
   <si>
-    <t>Voir le guide : prix rénovation maison au m2</t>
-  </si>
-  <si>
-    <t>Voir le guide : combien coûte une rénovation maison</t>
-  </si>
-  <si>
-    <t>Voir le guide : quel budget pour rénover une maison</t>
-  </si>
-  <si>
-    <t>Voir le guide : prix construction maison au m2</t>
-  </si>
-  <si>
-    <t>Voir le guide : prix maçonnerie au m2</t>
-  </si>
-  <si>
-    <t>Voir le guide : prix terrassement au m2</t>
-  </si>
-  <si>
-    <t>Voir le guide : combien coûte un maçon</t>
-  </si>
-  <si>
     <t>Voir le guide : comment choisir une entreprise de rénovation</t>
   </si>
   <si>
@@ -1292,6 +1361,27 @@
     <t>RK Pyrénées Construction avis à Toulouse</t>
   </si>
   <si>
+    <t>Voir le guide : étapes rénovation maison Toulouse</t>
+  </si>
+  <si>
+    <t>Voir le guide : comment préparer un projet de rénovation</t>
+  </si>
+  <si>
+    <t>Voir le guide : rénovation maison ancienne étapes</t>
+  </si>
+  <si>
+    <t>Voir le guide : étapes projet construction Toulouse</t>
+  </si>
+  <si>
+    <t>Voir le guide : comment choisir une entreprise de maçonnerie Toulouse</t>
+  </si>
+  <si>
+    <t>Voir le guide : comment préparer un chantier de terrassement</t>
+  </si>
+  <si>
+    <t>Voir le guide : comment choisir un professionnel pour un dallage extérieur</t>
+  </si>
+  <si>
     <t>Existing Page</t>
   </si>
   <si>
@@ -1313,22 +1403,25 @@
     <t>Faible effort (ajout d'une phrase), gain SEO ciblé sur une variante de requête déjà identifiée dans la recherche.</t>
   </si>
   <si>
-    <t>prix maçonnerie Toulouse / prix terrassement Toulouse / prix dalle béton m2 / prix extension maison Toulouse / extension maison prix m2</t>
-  </si>
-  <si>
-    <t>/services/maconnerie, /services/terrassement, /services/dallage, /services/extension</t>
-  </si>
-  <si>
-    <t>Aucune de ces 4 pages service ne mentionne le mot "prix" — l'information tarifaire n'existe que pour rénovation/construction/maçonnerie/terrassement, sous forme de guide national sans ancrage Toulouse (et aucun guide n'existe pour dallage/extension).</t>
-  </si>
-  <si>
-    <t>Ajouter un court paragraphe "facteurs de prix + devis gratuit" sur chaque page service concernée ; envisager /guides/prix-dallage et /guides/prix-extension si une source de prix fiable est trouvée.</t>
+    <t>prix maçonnerie Toulouse / prix terrassement Toulouse / prix dalle béton m2 / prix extension maison Toulouse / extension maison prix m2 / prix rénovation maison au m2 / prix construction maison au m2 / prix maçonnerie au m2 / prix terrassement au m2 / combien coûte une rénovation maison / combien coûte un maçon / quel budget pour rénover une maison</t>
+  </si>
+  <si>
+    <t>Aucune (les 4 anciens guides de prix ont été retirés du site)</t>
+  </si>
+  <si>
+    <t>DÉCISION CLIENT (2026-08-20) : aucun contenu tarifaire client, quel qu'il soit. Ce n'est plus un gap à combler — c'est un choix de stratégie assumé, à ne pas "corriger" sans nouvelle instruction du client.</t>
+  </si>
+  <si>
+    <t>Aucune — remplacé par des guides pratiques sans prix (voir /guides/etapes-renovation-maison, /guides/etapes-projet-construction, /guides/comment-choisir-entreprise-maconnerie-toulouse, /guides/comment-preparer-chantier-terrassement).</t>
   </si>
   <si>
     <t>COMMERCIAL</t>
   </si>
   <si>
-    <t>Intention commerciale forte (mot-clé "prix") non servie sur 4 pages service — écart structurel identifié pendant la vérification, pas une hypothèse.</t>
+    <t>N/A — WILL NOT FIX</t>
+  </si>
+  <si>
+    <t>Conservé comme mot-clé de recherche/opportunité dans ALL_KEYWORDS (Status = Research/Opportunity Only), jamais comme cible de contenu publié.</t>
   </si>
   <si>
     <t>Le terme "surélévation" (ajout d'étage) n'est jamais utilisé — la page reste générale ("agrandir une maison existante").</t>
@@ -1430,16 +1523,16 @@
     <t>Complètement indisponible dans cet environnement. Toutes les colonnes Trend/Trend Direction sont N/A pour cette raison, pas par omission.</t>
   </si>
   <si>
-    <t>Recherche de prix tiers (Effy, Hellowatt, Architecteo, La Maison Des Travaux)</t>
-  </si>
-  <si>
-    <t>Voir citations dans src/data/guides.ts (sourceNote par guide)</t>
-  </si>
-  <si>
-    <t>Fourchettes de prix nationales indicatives (rénovation €/m², extension €/m²), toujours citées avec attribution</t>
-  </si>
-  <si>
-    <t>Données nationales, non spécifiques à Toulouse, non vérifiées indépendamment, jamais présentées comme des tarifs RK Pyrénées</t>
+    <t>Recherche de prix tiers (Effy, Hellowatt, Architecteo, La Maison Des Travaux) — HISTORIQUE, PLUS UTILISÉ</t>
+  </si>
+  <si>
+    <t>N/A — retiré du site</t>
+  </si>
+  <si>
+    <t>Fourchettes de prix nationales indicatives (rénovation €/m², extension €/m²), utilisées dans les guides de prix d'origine.</t>
+  </si>
+  <si>
+    <t>Ces guides ont été retirés le 2026-08-20 (décision client : aucun contenu tarifaire client). Cette recherche reste documentée ici pour l'historique mais n'alimente plus aucune page du site actuel — voir src/data/guides.ts.</t>
   </si>
   <si>
     <t>Brief et échanges avec le client</t>
@@ -2260,7 +2353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA76"/>
+  <dimension ref="A1:AA83"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -4582,7 +4675,7 @@
         <v>90</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="S28" s="2" t="s">
         <v>91</v>
@@ -4597,7 +4690,7 @@
         <v>114</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="X28" s="2" t="s">
         <v>96</v>
@@ -4609,15 +4702,15 @@
         <v>98</v>
       </c>
       <c r="AA28" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>87</v>
@@ -4692,12 +4785,12 @@
         <v>98</v>
       </c>
       <c r="AA29" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>54</v>
@@ -4757,7 +4850,7 @@
         <v>92</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V30" s="2" t="s">
         <v>94</v>
@@ -4775,15 +4868,15 @@
         <v>98</v>
       </c>
       <c r="AA30" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>87</v>
@@ -4840,7 +4933,7 @@
         <v>92</v>
       </c>
       <c r="U31" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V31" s="2" t="s">
         <v>94</v>
@@ -4858,15 +4951,15 @@
         <v>98</v>
       </c>
       <c r="AA31" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>87</v>
@@ -4923,7 +5016,7 @@
         <v>92</v>
       </c>
       <c r="U32" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V32" s="2" t="s">
         <v>114</v>
@@ -4941,15 +5034,15 @@
         <v>98</v>
       </c>
       <c r="AA32" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>87</v>
@@ -4997,7 +5090,7 @@
         <v>90</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="S33" s="2" t="s">
         <v>91</v>
@@ -5006,13 +5099,13 @@
         <v>92</v>
       </c>
       <c r="U33" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V33" s="2" t="s">
         <v>114</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="X33" s="2" t="s">
         <v>96</v>
@@ -5024,15 +5117,15 @@
         <v>98</v>
       </c>
       <c r="AA33" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="34" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>87</v>
@@ -5089,7 +5182,7 @@
         <v>92</v>
       </c>
       <c r="U34" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V34" s="2" t="s">
         <v>94</v>
@@ -5107,12 +5200,12 @@
         <v>98</v>
       </c>
       <c r="AA34" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>61</v>
@@ -5172,7 +5265,7 @@
         <v>92</v>
       </c>
       <c r="U35" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="V35" s="2" t="s">
         <v>94</v>
@@ -5190,15 +5283,15 @@
         <v>98</v>
       </c>
       <c r="AA35" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>87</v>
@@ -5255,7 +5348,7 @@
         <v>92</v>
       </c>
       <c r="U36" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="V36" s="2" t="s">
         <v>94</v>
@@ -5273,15 +5366,15 @@
         <v>98</v>
       </c>
       <c r="AA36" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>87</v>
@@ -5338,7 +5431,7 @@
         <v>92</v>
       </c>
       <c r="U37" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="V37" s="2" t="s">
         <v>94</v>
@@ -5356,15 +5449,15 @@
         <v>98</v>
       </c>
       <c r="AA37" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="38" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>87</v>
@@ -5421,7 +5514,7 @@
         <v>92</v>
       </c>
       <c r="U38" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>94</v>
@@ -5439,15 +5532,15 @@
         <v>98</v>
       </c>
       <c r="AA38" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>87</v>
@@ -5495,7 +5588,7 @@
         <v>90</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="S39" s="2" t="s">
         <v>91</v>
@@ -5504,13 +5597,13 @@
         <v>92</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="V39" s="2" t="s">
         <v>114</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="X39" s="2" t="s">
         <v>96</v>
@@ -5522,12 +5615,12 @@
         <v>98</v>
       </c>
       <c r="AA39" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>42</v>
@@ -5581,13 +5674,13 @@
         <v>46</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="T40" s="2" t="s">
         <v>118</v>
       </c>
       <c r="U40" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="V40" s="2" t="s">
         <v>94</v>
@@ -5605,15 +5698,15 @@
         <v>98</v>
       </c>
       <c r="AA40" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>87</v>
@@ -5664,13 +5757,13 @@
         <v>46</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="T41" s="2" t="s">
         <v>118</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="V41" s="2" t="s">
         <v>94</v>
@@ -5688,15 +5781,15 @@
         <v>98</v>
       </c>
       <c r="AA41" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="42" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>87</v>
@@ -5744,22 +5837,22 @@
         <v>90</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="T42" s="2" t="s">
         <v>118</v>
       </c>
       <c r="U42" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="V42" s="2" t="s">
         <v>114</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="X42" s="2" t="s">
         <v>96</v>
@@ -5771,15 +5864,15 @@
         <v>98</v>
       </c>
       <c r="AA42" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="43" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>87</v>
@@ -5827,22 +5920,22 @@
         <v>90</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="T43" s="2" t="s">
         <v>118</v>
       </c>
       <c r="U43" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="V43" s="2" t="s">
         <v>114</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="X43" s="2" t="s">
         <v>96</v>
@@ -5854,7 +5947,7 @@
         <v>98</v>
       </c>
       <c r="AA43" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="44" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5913,13 +6006,13 @@
         <v>46</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="T44" s="2" t="s">
         <v>118</v>
       </c>
       <c r="U44" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="V44" s="2" t="s">
         <v>114</v>
@@ -5996,13 +6089,13 @@
         <v>46</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="T45" s="2" t="s">
         <v>118</v>
       </c>
       <c r="U45" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="V45" s="2" t="s">
         <v>114</v>
@@ -6408,22 +6501,22 @@
         <v>230</v>
       </c>
       <c r="R50" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="S50" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="S50" s="2" t="s">
+      <c r="T50" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="T50" s="2" t="s">
+      <c r="U50" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="U50" s="2" t="s">
-        <v>234</v>
-      </c>
       <c r="V50" s="2" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="W50" s="2" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="X50" s="2" t="s">
         <v>96</v>
@@ -6435,15 +6528,15 @@
         <v>98</v>
       </c>
       <c r="AA50" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>87</v>
@@ -6461,7 +6554,7 @@
         <v>226</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>228</v>
@@ -6491,22 +6584,22 @@
         <v>230</v>
       </c>
       <c r="R51" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="S51" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="S51" s="2" t="s">
+      <c r="T51" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="T51" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="U51" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="V51" s="2" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="W51" s="2" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="X51" s="2" t="s">
         <v>96</v>
@@ -6518,15 +6611,15 @@
         <v>98</v>
       </c>
       <c r="AA51" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="52" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>242</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>87</v>
@@ -6544,7 +6637,7 @@
         <v>226</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>228</v>
@@ -6568,28 +6661,28 @@
         <v>17</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q52" s="2" t="s">
         <v>230</v>
       </c>
       <c r="R52" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="S52" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="S52" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="T52" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="U52" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="V52" s="2" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="W52" s="2" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="X52" s="2" t="s">
         <v>96</v>
@@ -6601,15 +6694,15 @@
         <v>98</v>
       </c>
       <c r="AA52" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="53" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>87</v>
@@ -6621,7 +6714,7 @@
         <v>98</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>226</v>
@@ -6642,7 +6735,7 @@
         <v>17</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>17</v>
@@ -6657,22 +6750,22 @@
         <v>230</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>250</v>
+        <v>98</v>
       </c>
       <c r="S53" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="T53" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="T53" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="U53" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="V53" s="2" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="W53" s="2" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="X53" s="2" t="s">
         <v>96</v>
@@ -6684,15 +6777,15 @@
         <v>98</v>
       </c>
       <c r="AA53" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="54" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>87</v>
@@ -6704,29 +6797,29 @@
         <v>98</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>226</v>
       </c>
       <c r="H54" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M54" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="I54" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L54" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M54" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="N54" s="2" t="s">
         <v>17</v>
       </c>
@@ -6734,28 +6827,28 @@
         <v>17</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q54" s="2" t="s">
         <v>230</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>259</v>
+        <v>98</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="T54" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="U54" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="V54" s="2" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="W54" s="2" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="X54" s="2" t="s">
         <v>96</v>
@@ -6767,15 +6860,15 @@
         <v>98</v>
       </c>
       <c r="AA54" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="55" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>87</v>
@@ -6787,29 +6880,29 @@
         <v>98</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>226</v>
       </c>
       <c r="H55" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M55" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="I55" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L55" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M55" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="N55" s="2" t="s">
         <v>17</v>
       </c>
@@ -6817,28 +6910,28 @@
         <v>17</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="Q55" s="2" t="s">
         <v>230</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>265</v>
+        <v>98</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="T55" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="U55" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="V55" s="2" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="W55" s="2" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="X55" s="2" t="s">
         <v>96</v>
@@ -6850,15 +6943,15 @@
         <v>98</v>
       </c>
       <c r="AA55" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="56" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>87</v>
@@ -6870,7 +6963,7 @@
         <v>98</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>226</v>
@@ -6879,7 +6972,7 @@
         <v>227</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>17</v>
@@ -6891,7 +6984,7 @@
         <v>17</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>17</v>
@@ -6900,28 +6993,28 @@
         <v>17</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="Q56" s="2" t="s">
         <v>230</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>259</v>
+        <v>98</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="T56" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="U56" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="V56" s="2" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="W56" s="2" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="X56" s="2" t="s">
         <v>96</v>
@@ -6933,15 +7026,15 @@
         <v>98</v>
       </c>
       <c r="AA56" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="57" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>87</v>
@@ -6953,16 +7046,16 @@
         <v>98</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>226</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>17</v>
@@ -6974,7 +7067,7 @@
         <v>17</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>17</v>
@@ -6983,22 +7076,22 @@
         <v>17</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="Q57" s="2" t="s">
         <v>230</v>
       </c>
       <c r="R57" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="T57" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="U57" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="V57" s="2" t="s">
         <v>94</v>
@@ -7016,12 +7109,12 @@
         <v>98</v>
       </c>
       <c r="AA57" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="58" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>48</v>
@@ -7075,13 +7168,13 @@
         <v>28</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="T58" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="U58" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="V58" s="2" t="s">
         <v>94</v>
@@ -7099,12 +7192,12 @@
         <v>98</v>
       </c>
       <c r="AA58" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="59" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>12</v>
@@ -7158,13 +7251,13 @@
         <v>20</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="U59" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="V59" s="2" t="s">
         <v>94</v>
@@ -7173,24 +7266,24 @@
         <v>95</v>
       </c>
       <c r="X59" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="Y59" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="Z59" s="2" t="s">
         <v>98</v>
       </c>
       <c r="AA59" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="60" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>87</v>
@@ -7241,13 +7334,13 @@
         <v>20</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="U60" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="V60" s="2" t="s">
         <v>114</v>
@@ -7265,15 +7358,15 @@
         <v>98</v>
       </c>
       <c r="AA60" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="61" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>87</v>
@@ -7324,13 +7417,13 @@
         <v>20</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="U61" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="V61" s="2" t="s">
         <v>94</v>
@@ -7348,15 +7441,15 @@
         <v>98</v>
       </c>
       <c r="AA61" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="62" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>87</v>
@@ -7365,10 +7458,10 @@
         <v>88</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>24</v>
@@ -7389,7 +7482,7 @@
         <v>17</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="N62" s="2" t="s">
         <v>17</v>
@@ -7398,31 +7491,31 @@
         <v>17</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="Q62" s="2" t="s">
         <v>230</v>
       </c>
       <c r="R62" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="U62" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="V62" s="2" t="s">
         <v>114</v>
       </c>
       <c r="W62" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="X62" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="Y62" s="2" t="s">
         <v>97</v>
@@ -7431,15 +7524,15 @@
         <v>98</v>
       </c>
       <c r="AA62" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="63" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>87</v>
@@ -7448,10 +7541,10 @@
         <v>88</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>24</v>
@@ -7472,7 +7565,7 @@
         <v>17</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>17</v>
@@ -7481,31 +7574,31 @@
         <v>17</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="Q63" s="2" t="s">
         <v>230</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="U63" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="V63" s="2" t="s">
         <v>114</v>
       </c>
       <c r="W63" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="X63" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="Y63" s="2" t="s">
         <v>97</v>
@@ -7514,15 +7607,15 @@
         <v>98</v>
       </c>
       <c r="AA63" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="64" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>87</v>
@@ -7531,10 +7624,10 @@
         <v>88</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>24</v>
@@ -7555,7 +7648,7 @@
         <v>17</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="N64" s="2" t="s">
         <v>17</v>
@@ -7564,31 +7657,31 @@
         <v>17</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="Q64" s="2" t="s">
         <v>230</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="U64" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="V64" s="2" t="s">
         <v>114</v>
       </c>
       <c r="W64" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="X64" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="Y64" s="2" t="s">
         <v>97</v>
@@ -7597,15 +7690,15 @@
         <v>98</v>
       </c>
       <c r="AA64" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="65" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>87</v>
@@ -7614,10 +7707,10 @@
         <v>88</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>24</v>
@@ -7638,7 +7731,7 @@
         <v>17</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>17</v>
@@ -7647,31 +7740,31 @@
         <v>17</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="Q65" s="2" t="s">
         <v>230</v>
       </c>
       <c r="R65" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="U65" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="V65" s="2" t="s">
         <v>114</v>
       </c>
       <c r="W65" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="X65" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="Y65" s="2" t="s">
         <v>97</v>
@@ -7680,15 +7773,15 @@
         <v>98</v>
       </c>
       <c r="AA65" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="66" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>87</v>
@@ -7697,10 +7790,10 @@
         <v>88</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>24</v>
@@ -7721,7 +7814,7 @@
         <v>17</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="N66" s="2" t="s">
         <v>17</v>
@@ -7730,31 +7823,31 @@
         <v>17</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="Q66" s="2" t="s">
         <v>230</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="T66" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="U66" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="V66" s="2" t="s">
         <v>114</v>
       </c>
       <c r="W66" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="X66" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="Y66" s="2" t="s">
         <v>97</v>
@@ -7763,15 +7856,15 @@
         <v>98</v>
       </c>
       <c r="AA66" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="67" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>87</v>
@@ -7780,10 +7873,10 @@
         <v>88</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>24</v>
@@ -7804,7 +7897,7 @@
         <v>17</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>17</v>
@@ -7813,31 +7906,31 @@
         <v>17</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="Q67" s="2" t="s">
         <v>230</v>
       </c>
       <c r="R67" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="U67" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="V67" s="2" t="s">
         <v>114</v>
       </c>
       <c r="W67" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="X67" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="Y67" s="2" t="s">
         <v>97</v>
@@ -7846,15 +7939,15 @@
         <v>98</v>
       </c>
       <c r="AA67" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="68" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>87</v>
@@ -7863,10 +7956,10 @@
         <v>88</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>24</v>
@@ -7887,7 +7980,7 @@
         <v>17</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="N68" s="2" t="s">
         <v>17</v>
@@ -7896,31 +7989,31 @@
         <v>17</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="Q68" s="2" t="s">
         <v>230</v>
       </c>
       <c r="R68" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="U68" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="V68" s="2" t="s">
         <v>114</v>
       </c>
       <c r="W68" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="X68" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="Y68" s="2" t="s">
         <v>97</v>
@@ -7929,15 +8022,15 @@
         <v>98</v>
       </c>
       <c r="AA68" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="69" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>87</v>
@@ -7946,10 +8039,10 @@
         <v>88</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>24</v>
@@ -7970,7 +8063,7 @@
         <v>17</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="N69" s="2" t="s">
         <v>17</v>
@@ -7979,31 +8072,31 @@
         <v>17</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="Q69" s="2" t="s">
         <v>230</v>
       </c>
       <c r="R69" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="T69" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="U69" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="V69" s="2" t="s">
         <v>114</v>
       </c>
       <c r="W69" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="X69" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="Y69" s="2" t="s">
         <v>97</v>
@@ -8012,593 +8105,1174 @@
         <v>98</v>
       </c>
       <c r="AA69" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="70" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>87</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>226</v>
       </c>
       <c r="H70" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O70" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P70" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q70" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="I70" s="2" t="s">
+      <c r="R70" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="J70" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K70" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L70" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M70" s="2" t="s">
+      <c r="S70" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="N70" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="O70" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P70" s="2" t="s">
+      <c r="T70" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U70" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="Q70" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="R70" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="S70" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="T70" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="U70" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="V70" s="2" t="s">
         <v>114</v>
       </c>
       <c r="W70" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="X70" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="Y70" s="2" t="s">
         <v>97</v>
       </c>
       <c r="Z70" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="AA70" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="71" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>87</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>226</v>
       </c>
       <c r="H71" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M71" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="N71" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O71" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P71" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q71" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="I71" s="2" t="s">
+      <c r="R71" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="J71" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K71" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L71" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M71" s="2" t="s">
+      <c r="S71" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="N71" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="O71" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P71" s="2" t="s">
+      <c r="T71" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U71" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="Q71" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="R71" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="S71" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="T71" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="U71" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="V71" s="2" t="s">
         <v>114</v>
       </c>
       <c r="W71" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="X71" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="Y71" s="2" t="s">
         <v>97</v>
       </c>
       <c r="Z71" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="AA71" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="72" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>87</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>226</v>
       </c>
       <c r="H72" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O72" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q72" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="I72" s="2" t="s">
+      <c r="R72" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="J72" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K72" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L72" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M72" s="2" t="s">
+      <c r="S72" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="N72" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="O72" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P72" s="2" t="s">
+      <c r="T72" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U72" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="Q72" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="R72" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="S72" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="T72" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="U72" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="V72" s="2" t="s">
         <v>114</v>
       </c>
       <c r="W72" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="X72" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="Y72" s="2" t="s">
         <v>97</v>
       </c>
       <c r="Z72" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="AA72" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>87</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>226</v>
       </c>
       <c r="H73" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M73" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O73" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P73" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q73" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="I73" s="2" t="s">
+      <c r="R73" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="J73" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K73" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L73" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M73" s="2" t="s">
+      <c r="S73" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="N73" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="O73" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P73" s="2" t="s">
+      <c r="T73" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U73" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="Q73" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="R73" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="S73" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="T73" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="U73" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="V73" s="2" t="s">
         <v>114</v>
       </c>
       <c r="W73" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="X73" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="Y73" s="2" t="s">
         <v>97</v>
       </c>
       <c r="Z73" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="AA73" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>87</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>226</v>
       </c>
       <c r="H74" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O74" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P74" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q74" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="I74" s="2" t="s">
+      <c r="R74" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="J74" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K74" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L74" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M74" s="2" t="s">
+      <c r="S74" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="N74" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="O74" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P74" s="2" t="s">
+      <c r="T74" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U74" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="Q74" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="R74" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="S74" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="T74" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="U74" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="V74" s="2" t="s">
         <v>114</v>
       </c>
       <c r="W74" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="X74" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="Y74" s="2" t="s">
         <v>97</v>
       </c>
       <c r="Z74" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="AA74" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>87</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>226</v>
       </c>
       <c r="H75" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O75" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P75" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q75" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="I75" s="2" t="s">
+      <c r="R75" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="J75" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K75" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L75" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M75" s="2" t="s">
+      <c r="S75" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="N75" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="O75" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P75" s="2" t="s">
+      <c r="T75" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U75" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="Q75" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="R75" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="S75" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="T75" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="U75" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="V75" s="2" t="s">
         <v>114</v>
       </c>
       <c r="W75" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="X75" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="Y75" s="2" t="s">
         <v>97</v>
       </c>
       <c r="Z75" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="AA75" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>87</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>226</v>
       </c>
       <c r="H76" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q76" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="I76" s="2" t="s">
+      <c r="R76" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="J76" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K76" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M76" s="2" t="s">
+      <c r="S76" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="N76" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="O76" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P76" s="2" t="s">
+      <c r="T76" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U76" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="Q76" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="R76" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="S76" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="T76" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="U76" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="V76" s="2" t="s">
         <v>114</v>
       </c>
       <c r="W76" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="X76" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="Y76" s="2" t="s">
         <v>97</v>
       </c>
       <c r="Z76" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="AA76" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
+      </c>
+    </row>
+    <row r="77" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P77" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q77" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="R77" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="S77" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="T77" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="U77" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="V77" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="W77" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="X77" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="Y77" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="Z77" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA77" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="78" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M78" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O78" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P78" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q78" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="R78" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="S78" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="T78" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="U78" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="V78" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="W78" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="X78" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="Y78" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="Z78" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA78" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="79" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M79" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="N79" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P79" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q79" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="R79" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="S79" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="T79" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="U79" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="V79" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="W79" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="X79" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="Y79" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="Z79" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA79" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="80" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="W80" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="X80" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="Y80" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="Z80" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA80" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="81" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="N81" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O81" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P81" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q81" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="R81" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="S81" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="T81" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="U81" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="V81" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="W81" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="X81" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="Y81" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="Z81" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA81" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="82" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O82" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P82" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q82" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="R82" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="S82" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="T82" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="U82" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="V82" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="W82" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="X82" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="Y82" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="Z82" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA82" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="83" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="N83" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P83" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q83" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="R83" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="S83" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="T83" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="U83" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="V83" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="W83" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="X83" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="Y83" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="Z83" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA83" s="2" t="s">
+        <v>391</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AA1"/>
-  <conditionalFormatting sqref="U2:U76">
+  <conditionalFormatting sqref="U2:U83">
     <cfRule type="containsText" dxfId="0" priority="1">
       <formula>NOT(ISERROR(SEARCH("YES",U2)))</formula>
     </cfRule>
@@ -8606,7 +9280,7 @@
       <formula>NOT(ISERROR(SEARCH("NO",U2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q76">
+  <conditionalFormatting sqref="Q2:Q83">
     <cfRule type="containsText" dxfId="2" priority="1">
       <formula>NOT(ISERROR(SEARCH("P1",Q2)))</formula>
     </cfRule>
@@ -8618,7 +9292,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -8635,22 +9309,22 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>357</v>
+        <v>392</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>358</v>
+        <v>393</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>359</v>
+        <v>394</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>360</v>
+        <v>395</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>361</v>
+        <v>396</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>81</v>
@@ -8670,16 +9344,16 @@
         <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8696,16 +9370,16 @@
         <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>366</v>
+        <v>401</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8722,16 +9396,16 @@
         <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>367</v>
+        <v>402</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8748,16 +9422,16 @@
         <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>368</v>
+        <v>403</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8774,16 +9448,16 @@
         <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>369</v>
+        <v>404</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8800,16 +9474,16 @@
         <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>370</v>
+        <v>405</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8826,16 +9500,16 @@
         <v>24</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>371</v>
+        <v>406</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8852,16 +9526,16 @@
         <v>24</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8878,16 +9552,16 @@
         <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>374</v>
+        <v>409</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8904,16 +9578,16 @@
         <v>24</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8930,16 +9604,16 @@
         <v>24</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8956,16 +9630,16 @@
         <v>24</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>377</v>
+        <v>412</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8982,16 +9656,16 @@
         <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>378</v>
+        <v>413</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9008,16 +9682,16 @@
         <v>24</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>379</v>
+        <v>414</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9034,16 +9708,16 @@
         <v>24</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>380</v>
+        <v>415</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9060,16 +9734,16 @@
         <v>24</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>381</v>
+        <v>416</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9086,16 +9760,16 @@
         <v>24</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9112,16 +9786,16 @@
         <v>24</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>383</v>
+        <v>418</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9138,16 +9812,16 @@
         <v>24</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>384</v>
+        <v>419</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9164,16 +9838,16 @@
         <v>24</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>385</v>
+        <v>420</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9190,16 +9864,16 @@
         <v>24</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>386</v>
+        <v>421</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9216,16 +9890,16 @@
         <v>24</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>387</v>
+        <v>422</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9242,16 +9916,16 @@
         <v>24</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>388</v>
+        <v>423</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9268,16 +9942,16 @@
         <v>24</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>389</v>
+        <v>424</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9294,16 +9968,16 @@
         <v>24</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>390</v>
+        <v>425</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9320,21 +9994,21 @@
         <v>24</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>391</v>
+        <v>426</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>40</v>
@@ -9346,47 +10020,47 @@
         <v>24</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>392</v>
+        <v>427</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>163</v>
+        <v>54</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>393</v>
+        <v>428</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>59</v>
@@ -9398,21 +10072,21 @@
         <v>24</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>394</v>
+        <v>429</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>59</v>
@@ -9424,21 +10098,21 @@
         <v>24</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>395</v>
+        <v>430</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>365</v>
+        <v>408</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>59</v>
@@ -9450,73 +10124,73 @@
         <v>24</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>396</v>
+        <v>431</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>174</v>
+        <v>61</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>397</v>
+        <v>432</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>398</v>
+        <v>433</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>61</v>
+        <v>185</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>66</v>
@@ -9528,21 +10202,21 @@
         <v>24</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>399</v>
+        <v>434</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>66</v>
@@ -9554,99 +10228,99 @@
         <v>24</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G36" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>184</v>
+        <v>42</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>401</v>
+        <v>436</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>402</v>
+        <v>437</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="39" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>403</v>
+        <v>438</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
     </row>
     <row r="40" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>42</v>
+        <v>206</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>46</v>
@@ -9658,258 +10332,258 @@
         <v>24</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>404</v>
+        <v>439</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>365</v>
+        <v>408</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>46</v>
+        <v>213</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>405</v>
+        <v>440</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>46</v>
+        <v>213</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>406</v>
+        <v>441</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>46</v>
+        <v>213</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>407</v>
+        <v>442</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>46</v>
+        <v>213</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>408</v>
+        <v>443</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
     </row>
     <row r="45" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>206</v>
+        <v>268</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>46</v>
+        <v>272</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>24</v>
+        <v>226</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>409</v>
+        <v>444</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
     </row>
     <row r="46" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>209</v>
+        <v>48</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>213</v>
+        <v>28</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>410</v>
+        <v>445</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="47" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>217</v>
+        <v>12</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>213</v>
+        <v>20</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>411</v>
+        <v>446</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
     </row>
     <row r="48" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>220</v>
+        <v>286</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>213</v>
+        <v>20</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>365</v>
+        <v>408</v>
       </c>
     </row>
     <row r="49" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>222</v>
+        <v>289</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>213</v>
+        <v>20</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>413</v>
+        <v>446</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="50" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>224</v>
+        <v>354</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>231</v>
+        <v>358</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>28</v>
@@ -9918,24 +10592,24 @@
         <v>226</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="51" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>237</v>
+        <v>366</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>231</v>
+        <v>358</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>28</v>
@@ -9944,50 +10618,50 @@
         <v>226</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>415</v>
+        <v>449</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="52" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>242</v>
+        <v>368</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>231</v>
+        <v>370</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>226</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>416</v>
+        <v>450</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="53" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>247</v>
+        <v>373</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>35</v>
@@ -9996,24 +10670,24 @@
         <v>226</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>417</v>
+        <v>451</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="54" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>254</v>
+        <v>378</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>259</v>
+        <v>380</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>40</v>
@@ -10022,24 +10696,24 @@
         <v>226</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>418</v>
+        <v>452</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="55" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>262</v>
+        <v>383</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>265</v>
+        <v>385</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>59</v>
@@ -10048,172 +10722,42 @@
         <v>226</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>419</v>
+        <v>453</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="56" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>268</v>
+        <v>388</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>259</v>
+        <v>390</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>226</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>420</v>
+        <v>454</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -10241,13 +10785,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>425</v>
+        <v>455</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>426</v>
+        <v>456</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>427</v>
+        <v>457</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -10261,48 +10805,48 @@
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>428</v>
+        <v>458</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>429</v>
+        <v>459</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>430</v>
+        <v>460</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>429</v>
+        <v>459</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>431</v>
+        <v>461</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>432</v>
+        <v>462</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>433</v>
+        <v>463</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>434</v>
+        <v>464</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>435</v>
+        <v>465</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>436</v>
+        <v>466</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>230</v>
+        <v>467</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>437</v>
+        <v>468</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10313,7 +10857,7 @@
         <v>46</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>438</v>
+        <v>469</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>46</v>
@@ -10322,10 +10866,10 @@
         <v>24</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>439</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10336,53 +10880,53 @@
         <v>213</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>440</v>
+        <v>471</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>441</v>
+        <v>472</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>442</v>
+        <v>473</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>443</v>
+        <v>474</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>444</v>
+        <v>475</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>445</v>
+        <v>476</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>446</v>
+        <v>477</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>445</v>
+        <v>476</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>24</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>442</v>
+        <v>473</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>447</v>
+        <v>478</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>448</v>
+        <v>479</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>20</v>
@@ -10394,7 +10938,7 @@
         <v>230</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>449</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -10419,140 +10963,140 @@
         <v>82</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>450</v>
+        <v>481</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>451</v>
+        <v>482</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>452</v>
+        <v>483</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>453</v>
+        <v>484</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>454</v>
+        <v>485</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>455</v>
+        <v>486</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>456</v>
+        <v>487</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>457</v>
+        <v>488</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>458</v>
+        <v>489</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>459</v>
+        <v>490</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>456</v>
+        <v>487</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>461</v>
+        <v>492</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>462</v>
+        <v>493</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>463</v>
+        <v>494</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>464</v>
+        <v>495</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>456</v>
+        <v>487</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>465</v>
+        <v>496</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>466</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>467</v>
+        <v>498</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>468</v>
+        <v>499</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>456</v>
+        <v>487</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>469</v>
+        <v>500</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>470</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>471</v>
+        <v>502</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>472</v>
+        <v>503</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>456</v>
+        <v>487</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>473</v>
+        <v>504</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>474</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>475</v>
+        <v>506</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>476</v>
+        <v>507</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>477</v>
+        <v>508</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>478</v>
+        <v>509</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>479</v>
+        <v>510</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>480</v>
+        <v>511</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>481</v>
+        <v>512</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>456</v>
+        <v>487</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>482</v>
+        <v>513</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>483</v>
+        <v>514</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>484</v>
+        <v>515</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>17</v>
@@ -10561,10 +11105,10 @@
         <v>17</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>485</v>
+        <v>516</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>486</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>
